--- a/Analysis/Sensitivity_merec_entropy_arms_deepseek.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_deepseek.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -490,22 +490,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.30772</v>
+        <v>0.30838</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3299</v>
+        <v>0.33094</v>
       </c>
       <c r="G2" t="n">
-        <v>0.49478</v>
+        <v>0.49374</v>
       </c>
       <c r="H2" t="n">
         <v>0.8108999999999998</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08167999999999997</v>
+        <v>0.05846000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.93086</v>
+        <v>0.93018</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3894</v>
+        <v>0.36684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.41434</v>
+        <v>0.38822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5292199999999999</v>
+        <v>0.5261600000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.86668</v>
+        <v>0.84618</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08167999999999997</v>
+        <v>0.05846000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.93086</v>
+        <v>0.93018</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.93086</v>
+        <v>0.93018</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9424800000000001</v>
+        <v>0.94146</v>
       </c>
       <c r="G4" t="n">
-        <v>0.94148</v>
+        <v>0.9445399999999999</v>
       </c>
       <c r="H4" t="n">
         <v>0.9927800000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08167999999999997</v>
+        <v>0.05846000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.93086</v>
+        <v>0.93018</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +601,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08891999999999999</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08838</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.34404</v>
+        <v>0.34612</v>
       </c>
       <c r="H5" t="n">
-        <v>0.70766</v>
+        <v>0.70662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.26356</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.89388</v>
+        <v>0.90144</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.35248</v>
+        <v>0.3497400000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3764</v>
+        <v>0.3718</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5476800000000001</v>
+        <v>0.56206</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8399999999999999</v>
+        <v>0.8328199999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.26356</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.89388</v>
+        <v>0.90144</v>
       </c>
     </row>
     <row r="7">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.89388</v>
+        <v>0.90144</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9091400000000001</v>
+        <v>0.91476</v>
       </c>
       <c r="G7" t="n">
-        <v>0.92506</v>
+        <v>0.9322199999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>0.98254</v>
+        <v>0.98766</v>
       </c>
       <c r="I7" t="n">
-        <v>0.26356</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.89388</v>
+        <v>0.90144</v>
       </c>
     </row>
     <row r="8">
@@ -742,7 +742,7 @@
         <v>0.77782</v>
       </c>
       <c r="I8" t="n">
-        <v>0.18738</v>
+        <v>0.16618</v>
       </c>
       <c r="J8" t="n">
         <v>0.92608</v>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.43316</v>
+        <v>0.41196</v>
       </c>
       <c r="F9" t="n">
-        <v>0.46616</v>
+        <v>0.44308</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6</v>
+        <v>0.59076</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8748800000000001</v>
+        <v>0.8707800000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.18738</v>
+        <v>0.16618</v>
       </c>
       <c r="J9" t="n">
         <v>0.92608</v>
@@ -813,16 +813,16 @@
         <v>0.92608</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9343</v>
+        <v>0.93428</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9363400000000001</v>
+        <v>0.9363199999999999</v>
       </c>
       <c r="H10" t="n">
         <v>0.9815200000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.18738</v>
+        <v>0.16618</v>
       </c>
       <c r="J10" t="n">
         <v>0.92608</v>
@@ -862,7 +862,7 @@
         <v>0.7820199999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09627999999999992</v>
+        <v>0.07507999999999998</v>
       </c>
       <c r="J11" t="n">
         <v>0.90486</v>
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.35386</v>
+        <v>0.33266</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3728399999999999</v>
+        <v>0.3497400000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5353600000000001</v>
+        <v>0.5261400000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.81334</v>
+        <v>0.80924</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09627999999999992</v>
+        <v>0.07507999999999998</v>
       </c>
       <c r="J12" t="n">
         <v>0.90486</v>
@@ -933,7 +933,7 @@
         <v>0.90486</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9158199999999999</v>
+        <v>0.9158200000000001</v>
       </c>
       <c r="G13" t="n">
         <v>0.9117</v>
@@ -942,7 +942,7 @@
         <v>0.9774200000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09627999999999992</v>
+        <v>0.07507999999999998</v>
       </c>
       <c r="J13" t="n">
         <v>0.90486</v>
@@ -982,10 +982,10 @@
         <v>0.6932</v>
       </c>
       <c r="I14" t="n">
-        <v>0.16508</v>
+        <v>0.14664</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8986799999999999</v>
+        <v>0.89254</v>
       </c>
     </row>
     <row r="15">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2588</v>
+        <v>0.24036</v>
       </c>
       <c r="F15" t="n">
-        <v>0.28564</v>
+        <v>0.26206</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4871800000000001</v>
+        <v>0.49026</v>
       </c>
       <c r="H15" t="n">
-        <v>0.80616</v>
+        <v>0.78976</v>
       </c>
       <c r="I15" t="n">
-        <v>0.16508</v>
+        <v>0.14664</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8986799999999999</v>
+        <v>0.89254</v>
       </c>
     </row>
     <row r="16">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.8986799999999999</v>
+        <v>0.89254</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9111799999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.91578</v>
+        <v>0.9096399999999999</v>
       </c>
       <c r="H16" t="n">
         <v>0.9887</v>
       </c>
       <c r="I16" t="n">
-        <v>0.16508</v>
+        <v>0.14664</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8986799999999999</v>
+        <v>0.89254</v>
       </c>
     </row>
     <row r="17">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.08892</v>
+        <v>0.08821999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.08734</v>
       </c>
       <c r="G17" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7087</v>
+        <v>0.70766</v>
       </c>
       <c r="I17" t="n">
-        <v>0.26562</v>
+        <v>0.25878</v>
       </c>
       <c r="J17" t="n">
-        <v>0.89254</v>
+        <v>0.8959400000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.35454</v>
+        <v>0.347</v>
       </c>
       <c r="F18" t="n">
-        <v>0.37898</v>
+        <v>0.36874</v>
       </c>
       <c r="G18" t="n">
-        <v>0.54972</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8410399999999999</v>
+        <v>0.8297399999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.26562</v>
+        <v>0.25878</v>
       </c>
       <c r="J18" t="n">
-        <v>0.89254</v>
+        <v>0.8959400000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.89254</v>
+        <v>0.8959400000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9080999999999999</v>
+        <v>0.9106799999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.924</v>
       </c>
       <c r="H19" t="n">
-        <v>0.98254</v>
+        <v>0.98766</v>
       </c>
       <c r="I19" t="n">
-        <v>0.26562</v>
+        <v>0.25878</v>
       </c>
       <c r="J19" t="n">
-        <v>0.89254</v>
+        <v>0.8959400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Sensitivity_merec_entropy_arms_deepseek.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_deepseek.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.09372</v>
+        <v>0.09301999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09409999999999999</v>
+        <v>0.09408000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3369</v>
+        <v>0.3338</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6932</v>
+        <v>0.6953</v>
       </c>
       <c r="I14" t="n">
-        <v>0.14664</v>
+        <v>0.14254</v>
       </c>
       <c r="J14" t="n">
-        <v>0.89254</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="15">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.24036</v>
+        <v>0.23556</v>
       </c>
       <c r="F15" t="n">
-        <v>0.26206</v>
+        <v>0.25692</v>
       </c>
       <c r="G15" t="n">
-        <v>0.49026</v>
+        <v>0.4800000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.78976</v>
+        <v>0.78872</v>
       </c>
       <c r="I15" t="n">
-        <v>0.14664</v>
+        <v>0.14254</v>
       </c>
       <c r="J15" t="n">
-        <v>0.89254</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="16">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.89254</v>
+        <v>0.8939</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9111799999999999</v>
+        <v>0.9117</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9096399999999999</v>
+        <v>0.9116799999999999</v>
       </c>
       <c r="H16" t="n">
         <v>0.9887</v>
       </c>
       <c r="I16" t="n">
-        <v>0.14664</v>
+        <v>0.14254</v>
       </c>
       <c r="J16" t="n">
-        <v>0.89254</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="17">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.08821999999999999</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08734</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.342</v>
+        <v>0.34612</v>
       </c>
       <c r="H17" t="n">
-        <v>0.70766</v>
+        <v>0.70662</v>
       </c>
       <c r="I17" t="n">
-        <v>0.25878</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8959400000000001</v>
+        <v>0.90144</v>
       </c>
     </row>
     <row r="18">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.347</v>
+        <v>0.3497400000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.36874</v>
+        <v>0.3718</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.56206</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8297399999999999</v>
+        <v>0.8328199999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.25878</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8959400000000001</v>
+        <v>0.90144</v>
       </c>
     </row>
     <row r="19">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.8959400000000001</v>
+        <v>0.90144</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9106799999999999</v>
+        <v>0.91476</v>
       </c>
       <c r="G19" t="n">
-        <v>0.924</v>
+        <v>0.9322199999999998</v>
       </c>
       <c r="H19" t="n">
         <v>0.98766</v>
       </c>
       <c r="I19" t="n">
-        <v>0.25878</v>
+        <v>0.2594400000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8959400000000001</v>
+        <v>0.90144</v>
       </c>
     </row>
   </sheetData>
